--- a/reports/Debug-purgatory-20260104/For The Week Ending (Actual)_Visits.xlsx
+++ b/reports/Debug-purgatory-20260104/For The Week Ending (Actual)_Visits.xlsx
@@ -34,10 +34,10 @@
     <t>Purgatory Passes</t>
   </si>
   <si>
-    <t>Purgatory Tickets</t>
+    <t>Purgatory Coaster</t>
   </si>
   <si>
-    <t>Purgatory Coaster</t>
+    <t>Purgatory Tickets</t>
   </si>
   <si>
     <t>Purgatory Comp Tickets</t>
@@ -434,10 +434,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="2">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="C2" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>5</v>
@@ -448,13 +448,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="C3" s="2">
-        <v>2046</v>
+        <v>1</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -462,13 +462,13 @@
         <v>1</v>
       </c>
       <c r="B4" s="2">
-        <v>46023</v>
+        <v>46022</v>
       </c>
       <c r="C4" s="2">
-        <v>9</v>
+        <v>493</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -476,13 +476,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="2">
-        <v>46023</v>
+        <v>46022</v>
       </c>
       <c r="C5" s="2">
-        <v>1552</v>
+        <v>2030</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -504,10 +504,10 @@
         <v>1</v>
       </c>
       <c r="B7" s="2">
-        <v>46023</v>
+        <v>46024</v>
       </c>
       <c r="C7" s="2">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>5</v>
@@ -518,10 +518,10 @@
         <v>1</v>
       </c>
       <c r="B8" s="2">
-        <v>46026</v>
+        <v>46024</v>
       </c>
       <c r="C8" s="2">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>5</v>
@@ -532,10 +532,10 @@
         <v>1</v>
       </c>
       <c r="B9" s="2">
-        <v>46026</v>
+        <v>46025</v>
       </c>
       <c r="C9" s="2">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>5</v>
@@ -546,13 +546,13 @@
         <v>1</v>
       </c>
       <c r="B10" s="2">
-        <v>46020</v>
+        <v>46025</v>
       </c>
       <c r="C10" s="2">
-        <v>1</v>
+        <v>310</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -560,13 +560,13 @@
         <v>1</v>
       </c>
       <c r="B11" s="2">
-        <v>46023</v>
+        <v>46025</v>
       </c>
       <c r="C11" s="2">
-        <v>4</v>
+        <v>1100</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -574,10 +574,10 @@
         <v>1</v>
       </c>
       <c r="B12" s="2">
-        <v>46024</v>
+        <v>46020</v>
       </c>
       <c r="C12" s="2">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>5</v>
@@ -588,10 +588,10 @@
         <v>1</v>
       </c>
       <c r="B13" s="2">
-        <v>46026</v>
+        <v>46023</v>
       </c>
       <c r="C13" s="2">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>5</v>
@@ -602,10 +602,10 @@
         <v>1</v>
       </c>
       <c r="B14" s="2">
-        <v>46020</v>
+        <v>46024</v>
       </c>
       <c r="C14" s="2">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>5</v>
@@ -616,13 +616,13 @@
         <v>1</v>
       </c>
       <c r="B15" s="2">
-        <v>46020</v>
+        <v>46026</v>
       </c>
       <c r="C15" s="2">
-        <v>486</v>
+        <v>12</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -630,13 +630,13 @@
         <v>1</v>
       </c>
       <c r="B16" s="2">
-        <v>46021</v>
+        <v>46020</v>
       </c>
       <c r="C16" s="2">
-        <v>2287</v>
+        <v>5</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -644,13 +644,13 @@
         <v>1</v>
       </c>
       <c r="B17" s="2">
-        <v>46023</v>
+        <v>46020</v>
       </c>
       <c r="C17" s="2">
-        <v>1</v>
+        <v>2046</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -661,10 +661,10 @@
         <v>46023</v>
       </c>
       <c r="C18" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -672,13 +672,13 @@
         <v>1</v>
       </c>
       <c r="B19" s="2">
-        <v>46024</v>
+        <v>46023</v>
       </c>
       <c r="C19" s="2">
-        <v>1456</v>
+        <v>1552</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -686,10 +686,10 @@
         <v>1</v>
       </c>
       <c r="B20" s="2">
-        <v>46025</v>
+        <v>46023</v>
       </c>
       <c r="C20" s="2">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>5</v>
@@ -700,10 +700,10 @@
         <v>1</v>
       </c>
       <c r="B21" s="2">
-        <v>46025</v>
+        <v>46023</v>
       </c>
       <c r="C21" s="2">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>5</v>
@@ -714,10 +714,10 @@
         <v>1</v>
       </c>
       <c r="B22" s="2">
-        <v>46025</v>
+        <v>46026</v>
       </c>
       <c r="C22" s="2">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>5</v>
@@ -731,7 +731,7 @@
         <v>46026</v>
       </c>
       <c r="C23" s="2">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>5</v>
@@ -742,10 +742,10 @@
         <v>1</v>
       </c>
       <c r="B24" s="2">
-        <v>46026</v>
+        <v>46020</v>
       </c>
       <c r="C24" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>5</v>
@@ -756,10 +756,10 @@
         <v>1</v>
       </c>
       <c r="B25" s="2">
-        <v>46021</v>
+        <v>46020</v>
       </c>
       <c r="C25" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>5</v>
@@ -773,10 +773,10 @@
         <v>46021</v>
       </c>
       <c r="C26" s="2">
-        <v>1</v>
+        <v>417</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -784,13 +784,13 @@
         <v>1</v>
       </c>
       <c r="B27" s="2">
-        <v>46022</v>
+        <v>46021</v>
       </c>
       <c r="C27" s="2">
-        <v>493</v>
+        <v>696</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -801,10 +801,10 @@
         <v>46022</v>
       </c>
       <c r="C28" s="2">
-        <v>2030</v>
+        <v>63</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -812,10 +812,10 @@
         <v>1</v>
       </c>
       <c r="B29" s="2">
-        <v>46023</v>
+        <v>46022</v>
       </c>
       <c r="C29" s="2">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>5</v>
@@ -826,10 +826,10 @@
         <v>1</v>
       </c>
       <c r="B30" s="2">
-        <v>46024</v>
+        <v>46023</v>
       </c>
       <c r="C30" s="2">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>5</v>
@@ -843,10 +843,10 @@
         <v>46024</v>
       </c>
       <c r="C31" s="2">
-        <v>1</v>
+        <v>608</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -854,13 +854,13 @@
         <v>1</v>
       </c>
       <c r="B32" s="2">
-        <v>46025</v>
+        <v>46024</v>
       </c>
       <c r="C32" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -871,10 +871,10 @@
         <v>46025</v>
       </c>
       <c r="C33" s="2">
-        <v>310</v>
+        <v>110</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -885,10 +885,10 @@
         <v>46025</v>
       </c>
       <c r="C34" s="2">
-        <v>1100</v>
+        <v>1469</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -896,10 +896,10 @@
         <v>1</v>
       </c>
       <c r="B35" s="2">
-        <v>46020</v>
+        <v>46025</v>
       </c>
       <c r="C35" s="2">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>5</v>
@@ -910,13 +910,13 @@
         <v>1</v>
       </c>
       <c r="B36" s="2">
-        <v>46021</v>
+        <v>46026</v>
       </c>
       <c r="C36" s="2">
-        <v>1</v>
+        <v>906</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -924,10 +924,10 @@
         <v>1</v>
       </c>
       <c r="B37" s="2">
-        <v>46021</v>
+        <v>46026</v>
       </c>
       <c r="C37" s="2">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>5</v>
@@ -938,13 +938,13 @@
         <v>1</v>
       </c>
       <c r="B38" s="2">
-        <v>46022</v>
+        <v>46026</v>
       </c>
       <c r="C38" s="2">
-        <v>607</v>
+        <v>1</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -952,13 +952,13 @@
         <v>1</v>
       </c>
       <c r="B39" s="2">
-        <v>46022</v>
+        <v>46020</v>
       </c>
       <c r="C39" s="2">
-        <v>588</v>
+        <v>628</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -966,13 +966,13 @@
         <v>1</v>
       </c>
       <c r="B40" s="2">
-        <v>46023</v>
+        <v>46020</v>
       </c>
       <c r="C40" s="2">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -980,10 +980,10 @@
         <v>1</v>
       </c>
       <c r="B41" s="2">
-        <v>46024</v>
+        <v>46021</v>
       </c>
       <c r="C41" s="2">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>5</v>
@@ -994,10 +994,10 @@
         <v>1</v>
       </c>
       <c r="B42" s="2">
-        <v>46024</v>
+        <v>46021</v>
       </c>
       <c r="C42" s="2">
-        <v>1</v>
+        <v>612</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>5</v>
@@ -1008,10 +1008,10 @@
         <v>1</v>
       </c>
       <c r="B43" s="2">
-        <v>46024</v>
+        <v>46022</v>
       </c>
       <c r="C43" s="2">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>5</v>
@@ -1022,10 +1022,10 @@
         <v>1</v>
       </c>
       <c r="B44" s="2">
-        <v>46024</v>
+        <v>46023</v>
       </c>
       <c r="C44" s="2">
-        <v>89</v>
+        <v>1</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>5</v>
@@ -1036,13 +1036,13 @@
         <v>1</v>
       </c>
       <c r="B45" s="2">
-        <v>46025</v>
+        <v>46023</v>
       </c>
       <c r="C45" s="2">
-        <v>406</v>
+        <v>12</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1050,13 +1050,13 @@
         <v>1</v>
       </c>
       <c r="B46" s="2">
-        <v>46025</v>
+        <v>46023</v>
       </c>
       <c r="C46" s="2">
-        <v>2</v>
+        <v>72</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1064,10 +1064,10 @@
         <v>1</v>
       </c>
       <c r="B47" s="2">
-        <v>46025</v>
+        <v>46024</v>
       </c>
       <c r="C47" s="2">
-        <v>2</v>
+        <v>1445</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>5</v>
@@ -1078,10 +1078,10 @@
         <v>1</v>
       </c>
       <c r="B48" s="2">
-        <v>46026</v>
+        <v>46025</v>
       </c>
       <c r="C48" s="2">
-        <v>81</v>
+        <v>1</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>5</v>
@@ -1092,13 +1092,13 @@
         <v>1</v>
       </c>
       <c r="B49" s="2">
-        <v>46020</v>
+        <v>46026</v>
       </c>
       <c r="C49" s="2">
-        <v>628</v>
+        <v>30</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -1109,10 +1109,10 @@
         <v>46020</v>
       </c>
       <c r="C50" s="2">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -1123,7 +1123,7 @@
         <v>46021</v>
       </c>
       <c r="C51" s="2">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>5</v>
@@ -1137,7 +1137,7 @@
         <v>46021</v>
       </c>
       <c r="C52" s="2">
-        <v>612</v>
+        <v>51</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>5</v>
@@ -1151,10 +1151,10 @@
         <v>46022</v>
       </c>
       <c r="C53" s="2">
-        <v>1</v>
+        <v>607</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -1162,10 +1162,10 @@
         <v>1</v>
       </c>
       <c r="B54" s="2">
-        <v>46023</v>
+        <v>46022</v>
       </c>
       <c r="C54" s="2">
-        <v>1</v>
+        <v>588</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>5</v>
@@ -1179,10 +1179,10 @@
         <v>46023</v>
       </c>
       <c r="C55" s="2">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -1190,10 +1190,10 @@
         <v>1</v>
       </c>
       <c r="B56" s="2">
-        <v>46023</v>
+        <v>46024</v>
       </c>
       <c r="C56" s="2">
-        <v>72</v>
+        <v>1</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>5</v>
@@ -1207,7 +1207,7 @@
         <v>46024</v>
       </c>
       <c r="C57" s="2">
-        <v>1445</v>
+        <v>1</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>5</v>
@@ -1218,10 +1218,10 @@
         <v>1</v>
       </c>
       <c r="B58" s="2">
-        <v>46025</v>
+        <v>46024</v>
       </c>
       <c r="C58" s="2">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>5</v>
@@ -1232,10 +1232,10 @@
         <v>1</v>
       </c>
       <c r="B59" s="2">
-        <v>46026</v>
+        <v>46024</v>
       </c>
       <c r="C59" s="2">
-        <v>30</v>
+        <v>89</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>5</v>
@@ -1246,13 +1246,13 @@
         <v>1</v>
       </c>
       <c r="B60" s="2">
-        <v>46020</v>
+        <v>46025</v>
       </c>
       <c r="C60" s="2">
-        <v>1</v>
+        <v>406</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -1260,13 +1260,13 @@
         <v>1</v>
       </c>
       <c r="B61" s="2">
-        <v>46020</v>
+        <v>46025</v>
       </c>
       <c r="C61" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -1274,13 +1274,13 @@
         <v>1</v>
       </c>
       <c r="B62" s="2">
-        <v>46021</v>
+        <v>46025</v>
       </c>
       <c r="C62" s="2">
-        <v>417</v>
+        <v>2</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -1288,13 +1288,13 @@
         <v>1</v>
       </c>
       <c r="B63" s="2">
-        <v>46021</v>
+        <v>46026</v>
       </c>
       <c r="C63" s="2">
-        <v>696</v>
+        <v>81</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -1302,10 +1302,10 @@
         <v>1</v>
       </c>
       <c r="B64" s="2">
-        <v>46022</v>
+        <v>46020</v>
       </c>
       <c r="C64" s="2">
-        <v>63</v>
+        <v>575</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>5</v>
@@ -1316,10 +1316,10 @@
         <v>1</v>
       </c>
       <c r="B65" s="2">
-        <v>46022</v>
+        <v>46020</v>
       </c>
       <c r="C65" s="2">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>5</v>
@@ -1333,10 +1333,10 @@
         <v>46023</v>
       </c>
       <c r="C66" s="2">
-        <v>1</v>
+        <v>528</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -1344,13 +1344,13 @@
         <v>1</v>
       </c>
       <c r="B67" s="2">
-        <v>46024</v>
+        <v>46023</v>
       </c>
       <c r="C67" s="2">
-        <v>608</v>
+        <v>936</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -1361,10 +1361,10 @@
         <v>46024</v>
       </c>
       <c r="C68" s="2">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -1372,10 +1372,10 @@
         <v>1</v>
       </c>
       <c r="B69" s="2">
-        <v>46025</v>
+        <v>46024</v>
       </c>
       <c r="C69" s="2">
-        <v>110</v>
+        <v>1</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>5</v>
@@ -1389,7 +1389,7 @@
         <v>46025</v>
       </c>
       <c r="C70" s="2">
-        <v>1469</v>
+        <v>34</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>5</v>
@@ -1400,13 +1400,13 @@
         <v>1</v>
       </c>
       <c r="B71" s="2">
-        <v>46025</v>
+        <v>46026</v>
       </c>
       <c r="C71" s="2">
-        <v>72</v>
+        <v>311</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -1417,10 +1417,10 @@
         <v>46026</v>
       </c>
       <c r="C72" s="2">
-        <v>906</v>
+        <v>969</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -1428,10 +1428,10 @@
         <v>1</v>
       </c>
       <c r="B73" s="2">
-        <v>46026</v>
+        <v>46020</v>
       </c>
       <c r="C73" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>5</v>
@@ -1442,13 +1442,13 @@
         <v>1</v>
       </c>
       <c r="B74" s="2">
-        <v>46026</v>
+        <v>46020</v>
       </c>
       <c r="C74" s="2">
-        <v>1</v>
+        <v>486</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -1456,13 +1456,13 @@
         <v>1</v>
       </c>
       <c r="B75" s="2">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="C75" s="2">
-        <v>575</v>
+        <v>2287</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -1470,10 +1470,10 @@
         <v>1</v>
       </c>
       <c r="B76" s="2">
-        <v>46020</v>
+        <v>46023</v>
       </c>
       <c r="C76" s="2">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>5</v>
@@ -1487,10 +1487,10 @@
         <v>46023</v>
       </c>
       <c r="C77" s="2">
-        <v>528</v>
+        <v>8</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -1498,13 +1498,13 @@
         <v>1</v>
       </c>
       <c r="B78" s="2">
-        <v>46023</v>
+        <v>46024</v>
       </c>
       <c r="C78" s="2">
-        <v>936</v>
+        <v>1456</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -1512,10 +1512,10 @@
         <v>1</v>
       </c>
       <c r="B79" s="2">
-        <v>46024</v>
+        <v>46025</v>
       </c>
       <c r="C79" s="2">
-        <v>89</v>
+        <v>27</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>5</v>
@@ -1526,10 +1526,10 @@
         <v>1</v>
       </c>
       <c r="B80" s="2">
-        <v>46024</v>
+        <v>46025</v>
       </c>
       <c r="C80" s="2">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>5</v>
@@ -1543,7 +1543,7 @@
         <v>46025</v>
       </c>
       <c r="C81" s="2">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>5</v>
@@ -1557,10 +1557,10 @@
         <v>46026</v>
       </c>
       <c r="C82" s="2">
-        <v>311</v>
+        <v>1</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -1571,7 +1571,7 @@
         <v>46026</v>
       </c>
       <c r="C83" s="2">
-        <v>969</v>
+        <v>6</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>5</v>
